--- a/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
+++ b/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Library/CloudStorage/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853BFEFC-D2B5-A548-B488-6E7B65D7D185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A87561A-1DD7-6246-981C-42DFCC05E15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="760" windowWidth="29440" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
@@ -239,9 +239,6 @@
     <t>CO.AP</t>
   </si>
   <si>
-    <t>CO.PG</t>
-  </si>
-  <si>
     <t>CO.AD</t>
   </si>
   <si>
@@ -957,6 +954,9 @@
   </si>
   <si>
     <t>GC.ANT</t>
+  </si>
+  <si>
+    <t>CO.GG</t>
   </si>
 </sst>
 </file>
@@ -2047,10 +2047,10 @@
   <sheetData>
     <row r="2" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="22"/>
@@ -2060,39 +2060,39 @@
     </row>
     <row r="3" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>81</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F4" s="6">
         <v>0</v>
@@ -2102,16 +2102,16 @@
     </row>
     <row r="5" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -2121,16 +2121,16 @@
     </row>
     <row r="6" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F6" s="6">
         <v>0</v>
@@ -2140,16 +2140,16 @@
     </row>
     <row r="7" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F7" s="6">
         <v>0</v>
@@ -2159,16 +2159,16 @@
     </row>
     <row r="8" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="6">
         <v>0</v>
@@ -2178,16 +2178,16 @@
     </row>
     <row r="9" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>157</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F9" s="6">
         <v>0</v>
@@ -2197,16 +2197,16 @@
     </row>
     <row r="10" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F10" s="6">
         <v>0</v>
@@ -2216,16 +2216,16 @@
     </row>
     <row r="11" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F11" s="6">
         <v>0</v>
@@ -2235,16 +2235,16 @@
     </row>
     <row r="12" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>301</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>302</v>
       </c>
       <c r="F12" s="6">
         <v>0</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="13" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B13" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D13" s="23"/>
       <c r="E13" s="22"/>
@@ -2267,25 +2267,25 @@
     </row>
     <row r="14" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2293,11 +2293,11 @@
         <v>0</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F15" s="6">
         <v>8</v>
@@ -2312,13 +2312,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F16" s="6">
         <v>12</v>
@@ -2333,13 +2333,13 @@
         <v>2</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>160</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F17" s="6">
         <v>9.5</v>
@@ -2354,13 +2354,13 @@
         <v>3</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F18" s="6">
         <v>12</v>
@@ -2375,13 +2375,13 @@
         <v>4</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>161</v>
-      </c>
       <c r="E19" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F19" s="6">
         <v>9.5</v>
@@ -2396,13 +2396,13 @@
         <v>5</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F20" s="6">
         <v>8</v>
@@ -2417,13 +2417,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F21" s="6">
         <v>12</v>
@@ -2438,13 +2438,13 @@
         <v>7</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F22" s="6">
         <v>5</v>
@@ -2459,13 +2459,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F23" s="6">
         <v>10</v>
@@ -2480,13 +2480,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F24" s="9">
         <v>4</v>
@@ -2501,13 +2501,13 @@
         <v>22</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F25" s="9">
         <v>10</v>
@@ -2522,13 +2522,13 @@
         <v>23</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F26" s="9">
         <v>5</v>
@@ -2543,13 +2543,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F27" s="9">
         <v>4</v>
@@ -2564,11 +2564,11 @@
         <v>31</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F28" s="6">
         <v>28.5</v>
@@ -2577,7 +2577,7 @@
         <v>120</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2585,13 +2585,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>58</v>
@@ -2606,13 +2606,13 @@
         <v>33</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>58</v>
@@ -2627,13 +2627,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F31" s="6">
         <v>3</v>
@@ -2648,13 +2648,13 @@
         <v>35</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F32" s="6">
         <v>2.8</v>
@@ -2666,37 +2666,37 @@
     </row>
     <row r="33" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>205</v>
-      </c>
       <c r="E33" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F33" s="6">
         <v>1.4</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F34" s="6">
         <v>0</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="35" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B35" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="22"/>
@@ -2719,25 +2719,25 @@
     </row>
     <row r="36" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2745,11 +2745,11 @@
         <v>38</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F37" s="9">
         <v>1.4</v>
@@ -2764,13 +2764,13 @@
         <v>39</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F38" s="9">
         <v>1.4</v>
@@ -2785,13 +2785,13 @@
         <v>40</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F39" s="9">
         <v>2.8</v>
@@ -2806,13 +2806,13 @@
         <v>41</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F40" s="9">
         <v>3.4</v>
@@ -2821,21 +2821,21 @@
         <v>60</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F41" s="9">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>30</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2852,13 +2852,13 @@
         <v>16</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F42" s="9">
         <v>7</v>
@@ -2873,11 +2873,11 @@
         <v>46</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F43" s="9">
         <v>2.8</v>
@@ -2890,13 +2890,13 @@
         <v>47</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>58</v>
@@ -2913,13 +2913,13 @@
         <v>48</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F45" s="9">
         <v>2.8</v>
@@ -2934,13 +2934,13 @@
         <v>49</v>
       </c>
       <c r="C46" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D46" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>144</v>
-      </c>
       <c r="E46" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F46" s="9">
         <v>2.8</v>
@@ -2955,11 +2955,11 @@
         <v>42</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F47" s="6">
         <v>1.4</v>
@@ -2974,13 +2974,13 @@
         <v>43</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F48" s="6">
         <v>1.4</v>
@@ -2995,13 +2995,13 @@
         <v>45</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F49" s="6">
         <v>2.8</v>
@@ -3016,13 +3016,13 @@
         <v>44</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F50" s="6">
         <v>3.4</v>
@@ -3031,21 +3031,21 @@
         <v>60</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F51" s="6">
         <v>1</v>
@@ -3054,7 +3054,7 @@
         <v>30</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3062,13 +3062,13 @@
         <v>17</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F52" s="6">
         <v>5</v>
@@ -3080,14 +3080,14 @@
     </row>
     <row r="53" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D53" s="11"/>
       <c r="E53" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F53" s="6">
         <v>2.8</v>
@@ -3100,13 +3100,13 @@
         <v>50</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>58</v>
@@ -3123,13 +3123,13 @@
         <v>51</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F55" s="6">
         <v>2.8</v>
@@ -3144,13 +3144,13 @@
         <v>52</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F56" s="6">
         <v>2.8</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="57" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B57" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D57" s="23"/>
       <c r="E57" s="22"/>
@@ -3175,37 +3175,37 @@
     </row>
     <row r="58" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="59" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F59" s="9">
         <v>1</v>
@@ -3214,112 +3214,112 @@
         <v>30</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F60" s="9">
         <v>1.2</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F61" s="9">
         <v>0.4</v>
       </c>
       <c r="G61" s="9"/>
       <c r="H61" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F62" s="9">
         <v>0.4</v>
       </c>
       <c r="G62" s="9"/>
       <c r="H62" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" s="9">
         <v>1.2</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F64" s="9">
         <v>1.2</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3327,18 +3327,18 @@
         <v>62</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F65" s="6">
         <v>1</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3346,20 +3346,20 @@
         <v>63</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F66" s="6">
         <v>1</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3367,39 +3367,39 @@
         <v>64</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F67" s="6">
         <v>1.2</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F68" s="6">
         <v>1.2</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3407,20 +3407,20 @@
         <v>66</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F69" s="6">
         <v>0.8</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3428,70 +3428,70 @@
         <v>65</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F70" s="6">
         <v>0.8</v>
       </c>
       <c r="G70" s="6"/>
       <c r="H70" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="5" t="s">
-        <v>67</v>
+        <v>306</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F71" s="6">
         <v>1</v>
       </c>
       <c r="G71" s="6"/>
       <c r="H71" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F72" s="6">
         <v>0.8</v>
       </c>
       <c r="G72" s="6"/>
       <c r="H72" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B73" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D73" s="23"/>
       <c r="E73" s="22"/>
@@ -3501,25 +3501,25 @@
     </row>
     <row r="74" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G74" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H74" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E74" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F74" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G74" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H74" s="15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="75" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3527,13 +3527,13 @@
         <v>20</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F75" s="9">
         <v>2.8</v>
@@ -3542,21 +3542,21 @@
         <v>20</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C76" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D76" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>199</v>
-      </c>
       <c r="E76" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F76" s="9">
         <v>13</v>
@@ -3565,61 +3565,61 @@
         <v>100</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F77" s="9">
         <v>1</v>
       </c>
       <c r="G77" s="9"/>
       <c r="H77" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D78" s="13"/>
       <c r="E78" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F78" s="9">
         <v>2</v>
       </c>
       <c r="G78" s="9"/>
       <c r="H78" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F79" s="9">
         <v>1</v>
@@ -3629,16 +3629,16 @@
     </row>
     <row r="80" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>58</v>
@@ -3650,16 +3650,16 @@
     </row>
     <row r="81" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B81" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F81" s="9">
         <v>0</v>
@@ -3669,16 +3669,16 @@
     </row>
     <row r="82" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F82" s="9">
         <v>0</v>
@@ -3688,16 +3688,16 @@
     </row>
     <row r="83" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F83" s="6">
         <v>4</v>
@@ -3706,21 +3706,21 @@
         <v>20</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F84" s="6">
         <v>20</v>
@@ -3729,40 +3729,40 @@
         <v>100</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F85" s="6">
         <v>2</v>
       </c>
       <c r="G85" s="6"/>
       <c r="H85" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D86" s="13"/>
       <c r="E86" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F86" s="9">
         <v>1</v>
@@ -3772,14 +3772,14 @@
     </row>
     <row r="87" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D87" s="13"/>
       <c r="E87" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F87" s="9">
         <v>1</v>
@@ -3788,21 +3788,21 @@
         <v>97.5</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F88" s="9">
         <v>1.5</v>
@@ -3812,16 +3812,16 @@
     </row>
     <row r="89" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F89" s="9">
         <v>1</v>
@@ -3831,92 +3831,92 @@
     </row>
     <row r="90" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D90" s="13"/>
       <c r="E90" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F90" s="9">
         <v>1.2</v>
       </c>
       <c r="G90" s="9"/>
       <c r="H90" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F91" s="9">
         <v>1.2</v>
       </c>
       <c r="G91" s="9"/>
       <c r="H91" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F92" s="9">
         <v>2.9</v>
       </c>
       <c r="G92" s="9"/>
       <c r="H92" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F93" s="9">
         <v>1.2</v>
       </c>
       <c r="G93" s="9"/>
       <c r="H93" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B94" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D94" s="23"/>
       <c r="E94" s="22"/>
@@ -3926,363 +3926,363 @@
     </row>
     <row r="95" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F95" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G95" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H95" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="C95" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D95" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E95" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F95" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G95" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H95" s="15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="96" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D96" s="11"/>
       <c r="E96" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F96" s="6">
         <v>1.8</v>
       </c>
       <c r="G96" s="6"/>
       <c r="H96" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B97" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F97" s="6">
         <v>1.4</v>
       </c>
       <c r="G97" s="6"/>
       <c r="H97" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F98" s="6">
         <v>10</v>
       </c>
       <c r="G98" s="6"/>
       <c r="H98" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F99" s="6">
         <v>0.8</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B100" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F100" s="6">
         <v>1.2</v>
       </c>
       <c r="G100" s="6"/>
       <c r="H100" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B101" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F101" s="6">
         <v>1.2</v>
       </c>
       <c r="G101" s="6"/>
       <c r="H101" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B102" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F102" s="6">
         <v>2</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B103" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F103" s="9">
         <v>1.4</v>
       </c>
       <c r="G103" s="9"/>
       <c r="H103" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F104" s="9">
         <v>1.5</v>
       </c>
       <c r="G104" s="9"/>
       <c r="H104" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F105" s="9">
         <v>1</v>
       </c>
       <c r="G105" s="9"/>
       <c r="H105" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F106" s="9">
         <v>1.2</v>
       </c>
       <c r="G106" s="9"/>
       <c r="H106" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F107" s="9">
         <v>1</v>
       </c>
       <c r="G107" s="9"/>
       <c r="H107" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F108" s="9">
         <v>1.4</v>
       </c>
       <c r="G108" s="9"/>
       <c r="H108" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D109" s="11"/>
       <c r="E109" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F109" s="6">
         <v>3</v>
       </c>
       <c r="G109" s="6"/>
       <c r="H109" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F110" s="6">
         <v>2</v>
       </c>
       <c r="G110" s="6"/>
       <c r="H110" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F111" s="6">
         <v>1</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B112" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D112" s="23"/>
       <c r="E112" s="22"/>
@@ -4292,39 +4292,39 @@
     </row>
     <row r="113" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B113" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F113" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G113" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H113" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="C113" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D113" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E113" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F113" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G113" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H113" s="15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B114" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C114" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="D114" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="D114" s="13" t="s">
-        <v>291</v>
-      </c>
       <c r="E114" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F114" s="9">
         <v>11</v>
@@ -4333,21 +4333,21 @@
         <v>60</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B115" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F115" s="9">
         <v>2</v>
@@ -4356,84 +4356,84 @@
         <v>30</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B116" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C116" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C116" s="13" t="s">
-        <v>232</v>
-      </c>
       <c r="D116" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F116" s="9">
         <v>10</v>
       </c>
       <c r="G116" s="9"/>
       <c r="H116" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B117" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F117" s="9">
         <v>1.4</v>
       </c>
       <c r="G117" s="9"/>
       <c r="H117" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B118" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F118" s="9">
         <v>2</v>
       </c>
       <c r="G118" s="9"/>
       <c r="H118" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="119" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B119" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F119" s="6">
         <v>11</v>
@@ -4442,21 +4442,21 @@
         <v>60</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B120" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F120" s="6">
         <v>2</v>
@@ -4465,202 +4465,202 @@
         <v>30</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B121" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F121" s="6">
         <v>10</v>
       </c>
       <c r="G121" s="6"/>
       <c r="H121" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B122" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C122" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C122" s="11" t="s">
-        <v>236</v>
-      </c>
       <c r="D122" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F122" s="6">
         <v>1.4</v>
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B123" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F123" s="6">
         <v>2</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B124" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C124" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="C124" s="13" t="s">
-        <v>238</v>
       </c>
       <c r="D124" s="13"/>
       <c r="E124" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F124" s="9">
         <v>3</v>
       </c>
       <c r="G124" s="9"/>
       <c r="H124" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B125" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F125" s="9">
         <v>1.6</v>
       </c>
       <c r="G125" s="9"/>
       <c r="H125" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B126" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C126" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="C126" s="13" t="s">
-        <v>241</v>
-      </c>
       <c r="D126" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F126" s="9">
         <v>7</v>
       </c>
       <c r="G126" s="9"/>
       <c r="H126" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B127" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C127" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="C127" s="13" t="s">
-        <v>243</v>
-      </c>
       <c r="D127" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F127" s="9">
         <v>3</v>
       </c>
       <c r="G127" s="9"/>
       <c r="H127" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B128" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F128" s="9">
         <v>4</v>
       </c>
       <c r="G128" s="9"/>
       <c r="H128" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B129" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F129" s="9">
         <v>4</v>
       </c>
       <c r="G129" s="9"/>
       <c r="H129" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B130" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D130" s="23"/>
       <c r="E130" s="22"/>
@@ -4670,317 +4670,317 @@
     </row>
     <row r="131" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B131" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D131" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E131" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F131" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G131" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H131" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="C131" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D131" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E131" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F131" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G131" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H131" s="15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="132" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B132" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="C132" s="26" t="s">
         <v>261</v>
-      </c>
-      <c r="C132" s="26" t="s">
-        <v>262</v>
       </c>
       <c r="D132" s="26"/>
       <c r="E132" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F132" s="28">
         <v>70</v>
       </c>
       <c r="G132" s="27"/>
       <c r="H132" s="25" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B133" s="25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C133" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D133" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F133" s="28">
         <v>64</v>
       </c>
       <c r="G133" s="27"/>
       <c r="H133" s="25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="134" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B134" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F134" s="6">
         <v>5</v>
       </c>
       <c r="G134" s="6"/>
       <c r="H134" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="135" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B135" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F135" s="6">
         <v>5</v>
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="136" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B136" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C136" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D136" s="26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F136" s="28">
         <v>10</v>
       </c>
       <c r="G136" s="27"/>
       <c r="H136" s="25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B137" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F137" s="6">
         <v>14</v>
       </c>
       <c r="G137" s="6"/>
       <c r="H137" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="138" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B138" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F138" s="6">
         <v>14</v>
       </c>
       <c r="G138" s="6"/>
       <c r="H138" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="139" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B139" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F139" s="6">
         <v>14</v>
       </c>
       <c r="G139" s="6"/>
       <c r="H139" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="140" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B140" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F140" s="6">
         <v>14</v>
       </c>
       <c r="G140" s="6"/>
       <c r="H140" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="141" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B141" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F141" s="6">
         <v>14</v>
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="25" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="142" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B142" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D142" s="11"/>
       <c r="E142" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F142" s="6">
         <v>19</v>
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="143" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B143" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D143" s="11"/>
       <c r="E143" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F143" s="6">
         <v>40</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="144" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B144" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D144" s="11"/>
       <c r="E144" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F144" s="6">
         <v>19</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="145" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B145" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D145" s="11"/>
       <c r="E145" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F145" s="6">
         <v>40</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="146" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B146" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D146" s="23"/>
       <c r="E146" s="22"/>
@@ -4990,37 +4990,37 @@
     </row>
     <row r="147" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B147" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C147" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D147" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E147" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F147" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G147" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H147" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="C147" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D147" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E147" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F147" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G147" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H147" s="15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="148" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B148" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C148" s="26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D148" s="26"/>
       <c r="E148" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F148" s="28">
         <v>0</v>

--- a/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
+++ b/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Library/CloudStorage/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A87561A-1DD7-6246-981C-42DFCC05E15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B3161-895D-DF4B-905C-891163F654C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="760" windowWidth="29440" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
+    <workbookView xWindow="800" yWindow="760" windowWidth="29440" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
   <sheets>
     <sheet name="TR-1um_Drawing_Layer_DR_Table" sheetId="2" r:id="rId1"/>
@@ -929,12 +929,6 @@
     <t>PO.Z2</t>
   </si>
   <si>
-    <t>Electrical</t>
-  </si>
-  <si>
-    <t>ANT</t>
-  </si>
-  <si>
     <t>Prohibited</t>
   </si>
   <si>
@@ -957,6 +951,12 @@
   </si>
   <si>
     <t>CO.GG</t>
+  </si>
+  <si>
+    <t>Electrical / Optional</t>
+  </si>
+  <si>
+    <t>ANTE</t>
   </si>
 </sst>
 </file>
@@ -2050,7 +2050,7 @@
         <v>188</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="22"/>
@@ -2235,16 +2235,16 @@
     </row>
     <row r="12" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>261</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F12" s="6">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="71" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>146</v>
@@ -3473,7 +3473,7 @@
         <v>146</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>136</v>
@@ -3594,7 +3594,7 @@
         <v>124</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D78" s="13"/>
       <c r="E78" s="8" t="s">
@@ -3632,7 +3632,7 @@
         <v>211</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>143</v>
@@ -3656,7 +3656,7 @@
         <v>149</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>165</v>
@@ -3672,7 +3672,7 @@
         <v>218</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>159</v>
@@ -4781,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D136" s="26" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E136" s="25" t="s">
         <v>136</v>
@@ -4980,7 +4980,7 @@
         <v>188</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D146" s="23"/>
       <c r="E146" s="22"/>
@@ -5013,14 +5013,14 @@
     </row>
     <row r="148" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B148" s="25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C148" s="26" t="s">
-        <v>303</v>
+        <v>204</v>
       </c>
       <c r="D148" s="26"/>
       <c r="E148" s="25" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F148" s="28">
         <v>0</v>

--- a/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
+++ b/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Library/CloudStorage/Dropbox/91_OpenPDK/TR-1um/Document/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B3161-895D-DF4B-905C-891163F654C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439FB1C9-0C98-1F41-9D86-FF4ED4B90AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="760" windowWidth="29440" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
+    <workbookView xWindow="860" yWindow="760" windowWidth="29380" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
   <sheets>
     <sheet name="TR-1um_Drawing_Layer_DR_Table" sheetId="2" r:id="rId1"/>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F59" s="9">
         <v>1</v>

--- a/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
+++ b/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25997B7-96D7-0A45-B11D-707DCB591EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0EA5F8-2E12-1441-9B3B-125B5D4905D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="760" windowWidth="29380" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="311">
   <si>
     <t>WN.W1</t>
   </si>
@@ -957,6 +957,18 @@
   </si>
   <si>
     <t>ANTE</t>
+  </si>
+  <si>
+    <t>=AP.S1</t>
+  </si>
+  <si>
+    <t>=AN.S1</t>
+  </si>
+  <si>
+    <t>AP(M)</t>
+  </si>
+  <si>
+    <t>AN(M)</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1151,6 +1163,12 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2898,14 +2916,12 @@
       <c r="E44" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>58</v>
+      <c r="F44" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="G44" s="9"/>
+      <c r="H44" s="29" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2916,7 +2932,7 @@
         <v>142</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>134</v>
@@ -3108,14 +3124,12 @@
       <c r="E54" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>58</v>
+      <c r="F54" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="30" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3147,7 +3161,7 @@
         <v>145</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>134</v>

--- a/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
+++ b/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0EA5F8-2E12-1441-9B3B-125B5D4905D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCCECCD-2878-E140-B6F8-73D3EE4DA821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="760" windowWidth="29380" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
+    <workbookView xWindow="860" yWindow="700" windowWidth="29380" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
   <sheets>
     <sheet name="TR-1um_Drawing_Layer_DR_Table" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="310">
   <si>
     <t>WN.W1</t>
   </si>
@@ -581,9 +581,6 @@
     <t>Bevel</t>
   </si>
   <si>
-    <t>AP+AR</t>
-  </si>
-  <si>
     <t>WN-AC/AR related</t>
   </si>
   <si>
@@ -605,9 +602,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>AP+AC</t>
-  </si>
-  <si>
     <t>ECmin</t>
   </si>
   <si>
@@ -969,6 +963,9 @@
   </si>
   <si>
     <t>AN(M)</t>
+  </si>
+  <si>
+    <t>WN.Z3</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1196,7 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>636012</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>165275</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2050,7 +2047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4478C0F2-BA21-8B4B-B7C2-220C0E7FA6A8}">
-  <dimension ref="B2:H149"/>
+  <dimension ref="B2:H150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="4" customWidth="1"/>
@@ -2065,10 +2062,10 @@
   <sheetData>
     <row r="2" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="22"/>
@@ -2101,13 +2098,13 @@
     </row>
     <row r="4" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>159</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>171</v>
@@ -2120,13 +2117,13 @@
     </row>
     <row r="5" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>160</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>171</v>
@@ -2139,13 +2136,13 @@
     </row>
     <row r="6" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>220</v>
+        <v>149</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>171</v>
@@ -2158,13 +2155,13 @@
     </row>
     <row r="7" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>152</v>
+        <v>218</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>171</v>
@@ -2177,10 +2174,10 @@
     </row>
     <row r="8" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>152</v>
@@ -2196,13 +2193,13 @@
     </row>
     <row r="9" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>155</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>171</v>
@@ -2215,13 +2212,13 @@
     </row>
     <row r="10" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>295</v>
+        <v>175</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>261</v>
+        <v>155</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>171</v>
@@ -2234,13 +2231,13 @@
     </row>
     <row r="11" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>171</v>
@@ -2253,16 +2250,16 @@
     </row>
     <row r="12" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>300</v>
+        <v>156</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>299</v>
+        <v>171</v>
       </c>
       <c r="F12" s="6">
         <v>0</v>
@@ -2270,130 +2267,128 @@
       <c r="G12" s="6"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B13" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="22"/>
-    </row>
-    <row r="14" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
+    <row r="13" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B14" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="22"/>
+    </row>
+    <row r="15" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="6">
-        <v>8</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>158</v>
-      </c>
+      <c r="D16" s="11"/>
       <c r="E16" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F16" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>158</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F17" s="6">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="H17" s="7" t="s">
-        <v>12</v>
+      <c r="H17" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>158</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F18" s="6">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>160</v>
@@ -2402,145 +2397,145 @@
         <v>134</v>
       </c>
       <c r="F19" s="6">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>159</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F20" s="6">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F21" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F22" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>158</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F23" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="6">
+        <v>10</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="7" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F24" s="9">
-        <v>4</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>159</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F25" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>159</v>
@@ -2549,88 +2544,88 @@
         <v>136</v>
       </c>
       <c r="F26" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F27" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" s="9">
+        <v>4</v>
+      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="8" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="6">
-        <v>28.5</v>
-      </c>
-      <c r="G28" s="6">
-        <v>120</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>138</v>
-      </c>
+      <c r="D29" s="11"/>
       <c r="E29" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H29" s="5"/>
+        <v>135</v>
+      </c>
+      <c r="F29" s="6">
+        <v>28.5</v>
+      </c>
+      <c r="G29" s="6">
+        <v>120</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="30" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>58</v>
@@ -2642,10 +2637,10 @@
     </row>
     <row r="31" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>160</v>
@@ -2653,213 +2648,211 @@
       <c r="E31" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F31" s="6">
-        <v>3</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="F31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F32" s="6">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="5" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F33" s="6">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="5" t="s">
-        <v>202</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B35" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="22"/>
-    </row>
-    <row r="36" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="1" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B36" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="22"/>
+    </row>
+    <row r="37" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F37" s="9">
-        <v>1.4</v>
-      </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="38" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D38" s="13"/>
       <c r="E38" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F38" s="9">
         <v>1.4</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>140</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F39" s="9">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="G40" s="9">
-        <v>60</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="G40" s="9"/>
       <c r="H40" s="8" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="8" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F41" s="9">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="G41" s="9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>114</v>
@@ -2867,93 +2860,95 @@
     </row>
     <row r="42" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="8" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F42" s="9">
-        <v>7</v>
-      </c>
-      <c r="G42" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="G42" s="9">
+        <v>30</v>
+      </c>
       <c r="H42" s="8" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="8" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D43" s="13"/>
+        <v>140</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>158</v>
+      </c>
       <c r="E43" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F43" s="9">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="9"/>
-      <c r="H43" s="8"/>
+      <c r="H43" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="44" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>142</v>
-      </c>
+      <c r="D44" s="13"/>
       <c r="E44" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F44" s="9">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="G44" s="9"/>
-      <c r="H44" s="29" t="s">
-        <v>307</v>
-      </c>
+      <c r="H44" s="8"/>
     </row>
     <row r="45" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>142</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>309</v>
+        <v>142</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F45" s="9">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="G45" s="9"/>
-      <c r="H45" s="8" t="s">
-        <v>53</v>
+      <c r="H45" s="29" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>142</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>134</v>
@@ -2963,111 +2958,109 @@
       </c>
       <c r="G46" s="9"/>
       <c r="H46" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F47" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G47" s="9"/>
+      <c r="H47" s="8" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F47" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>143</v>
-      </c>
+      <c r="D48" s="11"/>
       <c r="E48" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F48" s="6">
         <v>1.4</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>143</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F49" s="6">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>207</v>
+        <v>140</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F50" s="6">
-        <v>3.4</v>
-      </c>
-      <c r="G50" s="6">
-        <v>60</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="G50" s="6"/>
       <c r="H50" s="5" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="5" t="s">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>144</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F51" s="6">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="G51" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>114</v>
@@ -3075,93 +3068,95 @@
     </row>
     <row r="52" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="5" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F52" s="6">
-        <v>5</v>
-      </c>
-      <c r="G52" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="G52" s="6">
+        <v>30</v>
+      </c>
       <c r="H52" s="5" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="5" t="s">
-        <v>164</v>
+        <v>17</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D53" s="11"/>
+        <v>143</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>192</v>
+      </c>
       <c r="E53" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F53" s="6">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G53" s="6"/>
-      <c r="H53" s="5"/>
+      <c r="H53" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="54" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="5" t="s">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D54" s="11" t="s">
-        <v>145</v>
-      </c>
+      <c r="D54" s="11"/>
       <c r="E54" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F54" s="6">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="G54" s="6"/>
-      <c r="H54" s="30" t="s">
-        <v>308</v>
-      </c>
+      <c r="H54" s="5"/>
     </row>
     <row r="55" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>145</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F55" s="6">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="G55" s="6"/>
-      <c r="H55" s="5" t="s">
-        <v>60</v>
+      <c r="H55" s="30" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>145</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>134</v>
@@ -3171,115 +3166,115 @@
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B57" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="D57" s="23"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="22"/>
-    </row>
-    <row r="58" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="1" t="s">
+    <row r="58" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B58" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="D58" s="23"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="22"/>
+    </row>
+    <row r="59" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D59" s="13"/>
-      <c r="E59" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F59" s="9">
-        <v>1</v>
-      </c>
-      <c r="G59" s="9"/>
-      <c r="H59" s="8" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>204</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="D60" s="13"/>
       <c r="E60" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F60" s="9">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F61" s="9">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G61" s="9"/>
       <c r="H61" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>134</v>
@@ -3289,161 +3284,161 @@
       </c>
       <c r="G62" s="9"/>
       <c r="H62" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="F63" s="9">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="8" t="s">
-        <v>191</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F64" s="9">
         <v>1.2</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F65" s="6">
-        <v>1</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="5" t="s">
-        <v>87</v>
+      <c r="B65" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F65" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="G65" s="9"/>
+      <c r="H65" s="8" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B66" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="11" t="s">
-        <v>146</v>
-      </c>
+      <c r="D66" s="11"/>
       <c r="E66" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F66" s="6">
         <v>1</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D67" s="11"/>
+        <v>146</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="E67" s="5" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="F67" s="6">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="11" t="s">
-        <v>176</v>
-      </c>
+      <c r="D68" s="11"/>
       <c r="E68" s="5" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="F68" s="6">
         <v>1.2</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>136</v>
       </c>
       <c r="F69" s="6">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>136</v>
@@ -3453,128 +3448,126 @@
       </c>
       <c r="G70" s="6"/>
       <c r="H70" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="5" t="s">
-        <v>304</v>
+        <v>65</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F71" s="6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G71" s="6"/>
       <c r="H71" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="5" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>301</v>
+        <v>212</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F72" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G72" s="6"/>
       <c r="H72" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F73" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="G73" s="6"/>
+      <c r="H73" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B73" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D73" s="23"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="22"/>
-    </row>
-    <row r="74" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="15" t="s">
+    <row r="74" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B74" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D74" s="23"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="22"/>
+    </row>
+    <row r="75" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C75" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D74" s="16" t="s">
+      <c r="D75" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E75" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F75" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G74" s="17" t="s">
+      <c r="G75" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H74" s="15" t="s">
+      <c r="H75" s="15" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F75" s="9">
-        <v>2.8</v>
-      </c>
-      <c r="G75" s="9">
-        <v>20</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="8" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F76" s="9">
-        <v>13</v>
+        <v>2.8</v>
       </c>
       <c r="G76" s="9">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>114</v>
@@ -3582,115 +3575,119 @@
     </row>
     <row r="77" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" s="8" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F77" s="9">
-        <v>1</v>
-      </c>
-      <c r="G77" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="G77" s="9">
+        <v>100</v>
+      </c>
       <c r="H77" s="8" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="8" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="D78" s="13"/>
+        <v>202</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>149</v>
+      </c>
       <c r="E78" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F78" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" s="9"/>
       <c r="H78" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>180</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D79" s="13"/>
       <c r="E79" s="8" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="F79" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="9"/>
-      <c r="H79" s="8"/>
+      <c r="H79" s="8" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="80" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="8" t="s">
-        <v>211</v>
+        <v>121</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>302</v>
+        <v>149</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>58</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="F80" s="9">
+        <v>1</v>
+      </c>
+      <c r="G80" s="9"/>
       <c r="H80" s="8"/>
     </row>
     <row r="81" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B81" s="8" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>149</v>
+        <v>300</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>302</v>
+        <v>143</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="F81" s="9">
-        <v>0</v>
-      </c>
-      <c r="G81" s="9"/>
+        <v>134</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="H81" s="8"/>
     </row>
     <row r="82" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>302</v>
+        <v>149</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>159</v>
+        <v>300</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F82" s="9">
         <v>0</v>
@@ -3699,46 +3696,42 @@
       <c r="H82" s="8"/>
     </row>
     <row r="83" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D83" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F83" s="6">
-        <v>4</v>
-      </c>
-      <c r="G83" s="6">
-        <v>20</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="B83" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F83" s="9">
+        <v>0</v>
+      </c>
+      <c r="G83" s="9"/>
+      <c r="H83" s="8"/>
     </row>
     <row r="84" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F84" s="6">
+        <v>4</v>
+      </c>
+      <c r="G84" s="6">
         <v>20</v>
-      </c>
-      <c r="G84" s="6">
-        <v>100</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>114</v>
@@ -3746,331 +3739,333 @@
     </row>
     <row r="85" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F85" s="6">
+        <v>20</v>
+      </c>
+      <c r="G85" s="6">
+        <v>100</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F86" s="6">
         <v>2</v>
       </c>
-      <c r="G85" s="6"/>
-      <c r="H85" s="5" t="s">
+      <c r="G86" s="6"/>
+      <c r="H86" s="5" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="86" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D86" s="13"/>
-      <c r="E86" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F86" s="9">
-        <v>1</v>
-      </c>
-      <c r="G86" s="9"/>
-      <c r="H86" s="8"/>
     </row>
     <row r="87" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D87" s="13"/>
       <c r="E87" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F87" s="9">
         <v>1</v>
       </c>
-      <c r="G87" s="9">
-        <v>97.5</v>
-      </c>
-      <c r="H87" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="G87" s="9"/>
+      <c r="H87" s="8"/>
     </row>
     <row r="88" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>168</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="D88" s="13"/>
       <c r="E88" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F88" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="G88" s="9"/>
-      <c r="H88" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="G88" s="9">
+        <v>97.5</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="89" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>150</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>136</v>
       </c>
       <c r="F89" s="9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G89" s="9"/>
       <c r="H89" s="8"/>
     </row>
     <row r="90" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="8" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D90" s="13"/>
+        <v>150</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="E90" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F90" s="9">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G90" s="9"/>
-      <c r="H90" s="8" t="s">
-        <v>97</v>
-      </c>
+      <c r="H90" s="8"/>
     </row>
     <row r="91" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D91" s="13" t="s">
-        <v>151</v>
-      </c>
+      <c r="D91" s="13"/>
       <c r="E91" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F91" s="9">
         <v>1.2</v>
       </c>
       <c r="G91" s="9"/>
       <c r="H91" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>151</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F92" s="9">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="G92" s="9"/>
       <c r="H92" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C93" s="13" t="s">
         <v>151</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>136</v>
       </c>
       <c r="F93" s="9">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="G93" s="9"/>
       <c r="H93" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F94" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="G94" s="9"/>
+      <c r="H94" s="8" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B94" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C94" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="D94" s="23"/>
-      <c r="E94" s="22"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="22"/>
-    </row>
-    <row r="95" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="15" t="s">
+    <row r="95" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B95" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D95" s="23"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="24"/>
+      <c r="H95" s="22"/>
+    </row>
+    <row r="96" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C95" s="16" t="s">
+      <c r="C96" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D95" s="16" t="s">
+      <c r="D96" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E95" s="15" t="s">
+      <c r="E96" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="F95" s="17" t="s">
+      <c r="F96" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G95" s="17" t="s">
+      <c r="G96" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H95" s="15" t="s">
+      <c r="H96" s="15" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D96" s="11"/>
-      <c r="E96" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F96" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="G96" s="6"/>
-      <c r="H96" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B97" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D97" s="11" t="s">
-        <v>152</v>
-      </c>
+      <c r="D97" s="11"/>
       <c r="E97" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F97" s="6">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="G97" s="6"/>
       <c r="H97" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="5" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>134</v>
       </c>
       <c r="F98" s="6">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="G98" s="6"/>
       <c r="H98" s="5" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F99" s="6">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="5" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B100" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>152</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>148</v>
       </c>
       <c r="F100" s="6">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G100" s="6"/>
       <c r="H100" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B101" s="5" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>152</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>148</v>
@@ -4080,292 +4075,290 @@
       </c>
       <c r="G101" s="6"/>
       <c r="H101" s="5" t="s">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B102" s="5" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="F102" s="6">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F103" s="6">
+        <v>2</v>
+      </c>
+      <c r="G103" s="6"/>
+      <c r="H103" s="5" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B103" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D103" s="13"/>
-      <c r="E103" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F103" s="9">
-        <v>1.4</v>
-      </c>
-      <c r="G103" s="9"/>
-      <c r="H103" s="8" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C104" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="D104" s="13" t="s">
-        <v>155</v>
-      </c>
+      <c r="D104" s="13"/>
       <c r="E104" s="8" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="F104" s="9">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G104" s="9"/>
       <c r="H104" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C105" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F105" s="9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G105" s="9"/>
       <c r="H105" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="8" t="s">
-        <v>219</v>
+        <v>76</v>
       </c>
       <c r="C106" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F106" s="9">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G106" s="9"/>
       <c r="H106" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="8" t="s">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="C107" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="E107" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F107" s="9">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G107" s="9"/>
       <c r="H107" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C108" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F108" s="9">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G108" s="9"/>
       <c r="H108" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F109" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="G109" s="9"/>
+      <c r="H109" s="8" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C109" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D109" s="11"/>
-      <c r="E109" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F109" s="6">
-        <v>3</v>
-      </c>
-      <c r="G109" s="6"/>
-      <c r="H109" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="5" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D110" s="11" t="s">
-        <v>156</v>
-      </c>
+      <c r="D110" s="11"/>
       <c r="E110" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F110" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G110" s="6"/>
       <c r="H110" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F111" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F112" s="6">
+        <v>1</v>
+      </c>
+      <c r="G112" s="6"/>
+      <c r="H112" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="112" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B112" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C112" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="D112" s="23"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="24"/>
-      <c r="G112" s="24"/>
-      <c r="H112" s="22"/>
-    </row>
     <row r="113" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B113" s="15" t="s">
+      <c r="B113" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="D113" s="23"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="22"/>
+    </row>
+    <row r="114" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B114" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C113" s="16" t="s">
+      <c r="C114" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="16" t="s">
+      <c r="D114" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E113" s="15" t="s">
+      <c r="E114" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="F113" s="17" t="s">
+      <c r="F114" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G113" s="17" t="s">
+      <c r="G114" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H113" s="15" t="s">
+      <c r="H114" s="15" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="114" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B114" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F114" s="9">
-        <v>11</v>
-      </c>
-      <c r="G114" s="9">
-        <v>60</v>
-      </c>
-      <c r="H114" s="8" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B115" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F115" s="9">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G115" s="9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>114</v>
@@ -4373,108 +4366,108 @@
     </row>
     <row r="116" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B116" s="8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>143</v>
+        <v>290</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F116" s="9">
-        <v>10</v>
-      </c>
-      <c r="G116" s="9"/>
+        <v>2</v>
+      </c>
+      <c r="G116" s="9">
+        <v>30</v>
+      </c>
       <c r="H116" s="8" t="s">
-        <v>258</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B117" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="F117" s="9">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="G117" s="9"/>
       <c r="H117" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B118" s="8" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="F118" s="9">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G118" s="9"/>
       <c r="H118" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="119" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B119" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F119" s="6">
-        <v>11</v>
-      </c>
-      <c r="G119" s="6">
-        <v>60</v>
-      </c>
-      <c r="H119" s="5" t="s">
-        <v>114</v>
+      <c r="B119" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F119" s="9">
+        <v>2</v>
+      </c>
+      <c r="G119" s="9"/>
+      <c r="H119" s="8" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B120" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F120" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G120" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H120" s="5" t="s">
         <v>114</v>
@@ -4482,179 +4475,181 @@
     </row>
     <row r="121" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B121" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F121" s="6">
-        <v>10</v>
-      </c>
-      <c r="G121" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="G121" s="6">
+        <v>30</v>
+      </c>
       <c r="H121" s="5" t="s">
-        <v>257</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B122" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="F122" s="6">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B123" s="5" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="F123" s="6">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B124" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="C124" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="D124" s="13"/>
-      <c r="E124" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F124" s="9">
-        <v>3</v>
-      </c>
-      <c r="G124" s="9"/>
-      <c r="H124" s="8" t="s">
-        <v>253</v>
+      <c r="B124" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F124" s="6">
+        <v>2</v>
+      </c>
+      <c r="G124" s="6"/>
+      <c r="H124" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B125" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>237</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="D125" s="13"/>
       <c r="E125" s="8" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="F125" s="9">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="G125" s="9"/>
       <c r="H125" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B126" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F126" s="9">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="G126" s="9"/>
       <c r="H126" s="8" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B127" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F127" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G127" s="9"/>
       <c r="H127" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B128" s="8" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F128" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G128" s="9"/>
       <c r="H128" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B129" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E129" s="8" t="s">
         <v>136</v>
@@ -4664,115 +4659,115 @@
       </c>
       <c r="G129" s="9"/>
       <c r="H129" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B130" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C130" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="D130" s="23"/>
-      <c r="E130" s="22"/>
-      <c r="F130" s="24"/>
-      <c r="G130" s="24"/>
-      <c r="H130" s="22"/>
+      <c r="B130" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F130" s="9">
+        <v>4</v>
+      </c>
+      <c r="G130" s="9"/>
+      <c r="H130" s="8" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="131" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B131" s="15" t="s">
+      <c r="B131" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="D131" s="23"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="24"/>
+      <c r="G131" s="24"/>
+      <c r="H131" s="22"/>
+    </row>
+    <row r="132" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B132" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C131" s="16" t="s">
+      <c r="C132" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D131" s="16" t="s">
+      <c r="D132" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E131" s="15" t="s">
+      <c r="E132" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="F131" s="17" t="s">
+      <c r="F132" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G131" s="17" t="s">
+      <c r="G132" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H131" s="15" t="s">
+      <c r="H132" s="15" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="132" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B132" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="C132" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="D132" s="26"/>
-      <c r="E132" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="F132" s="28">
-        <v>70</v>
-      </c>
-      <c r="G132" s="27"/>
-      <c r="H132" s="25" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="133" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B133" s="25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C133" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="D133" s="26" t="s">
-        <v>261</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D133" s="26"/>
       <c r="E133" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F133" s="28">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G133" s="27"/>
       <c r="H133" s="25" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B134" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C134" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D134" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F134" s="6">
-        <v>5</v>
-      </c>
-      <c r="G134" s="6"/>
-      <c r="H134" s="5" t="s">
-        <v>276</v>
+      <c r="B134" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="D134" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E134" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F134" s="28">
+        <v>64</v>
+      </c>
+      <c r="G134" s="27"/>
+      <c r="H134" s="25" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="135" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B135" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C135" s="11" t="s">
         <v>264</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>148</v>
@@ -4782,60 +4777,60 @@
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="136" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B136" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="C136" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="D136" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="E136" s="25" t="s">
+      <c r="B136" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F136" s="6">
+        <v>5</v>
+      </c>
+      <c r="G136" s="6"/>
+      <c r="H136" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B137" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="C137" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="D137" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="E137" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="F136" s="28">
+      <c r="F137" s="28">
         <v>10</v>
       </c>
-      <c r="G136" s="27"/>
-      <c r="H136" s="25" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="137" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B137" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C137" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D137" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F137" s="6">
-        <v>14</v>
-      </c>
-      <c r="G137" s="6"/>
-      <c r="H137" s="5" t="s">
-        <v>280</v>
+      <c r="G137" s="27"/>
+      <c r="H137" s="25" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="138" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B138" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>134</v>
@@ -4845,18 +4840,18 @@
       </c>
       <c r="G138" s="6"/>
       <c r="H138" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="139" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B139" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>134</v>
@@ -4866,18 +4861,18 @@
       </c>
       <c r="G139" s="6"/>
       <c r="H139" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="140" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B140" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>134</v>
@@ -4886,19 +4881,19 @@
         <v>14</v>
       </c>
       <c r="G140" s="6"/>
-      <c r="H140" s="25" t="s">
-        <v>278</v>
+      <c r="H140" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="141" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B141" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>134</v>
@@ -4908,146 +4903,167 @@
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="25" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="142" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B142" s="5" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C142" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D142" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D142" s="11"/>
       <c r="E142" s="5" t="s">
-        <v>294</v>
+        <v>134</v>
       </c>
       <c r="F142" s="6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G142" s="6"/>
-      <c r="H142" s="5" t="s">
-        <v>282</v>
+      <c r="H142" s="25" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B143" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D143" s="11"/>
       <c r="E143" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F143" s="6">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="144" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B144" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D144" s="11"/>
       <c r="E144" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F144" s="6">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="145" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B145" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D145" s="11"/>
       <c r="E145" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F145" s="6">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="146" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B146" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C146" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="D146" s="23"/>
-      <c r="E146" s="22"/>
-      <c r="F146" s="24"/>
-      <c r="G146" s="24"/>
-      <c r="H146" s="22"/>
+      <c r="B146" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D146" s="11"/>
+      <c r="E146" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F146" s="6">
+        <v>40</v>
+      </c>
+      <c r="G146" s="6"/>
+      <c r="H146" s="5" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="147" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B147" s="15" t="s">
+      <c r="B147" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C147" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="D147" s="23"/>
+      <c r="E147" s="22"/>
+      <c r="F147" s="24"/>
+      <c r="G147" s="24"/>
+      <c r="H147" s="22"/>
+    </row>
+    <row r="148" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B148" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C147" s="16" t="s">
+      <c r="C148" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D147" s="16" t="s">
+      <c r="D148" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E147" s="15" t="s">
+      <c r="E148" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="F147" s="17" t="s">
+      <c r="F148" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G147" s="17" t="s">
+      <c r="G148" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H147" s="15" t="s">
+      <c r="H148" s="15" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="148" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B148" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="C148" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="D148" s="26"/>
-      <c r="E148" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="F148" s="28">
+    <row r="149" spans="2:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="B149" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="C149" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="D149" s="26"/>
+      <c r="E149" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="F149" s="28">
         <v>0</v>
       </c>
-      <c r="G148" s="27"/>
-      <c r="H148" s="25"/>
-    </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B149" s="25"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="25"/>
-      <c r="F149" s="28"/>
       <c r="G149" s="27"/>
       <c r="H149" s="25"/>
+    </row>
+    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B150" s="25"/>
+      <c r="C150" s="26"/>
+      <c r="D150" s="26"/>
+      <c r="E150" s="25"/>
+      <c r="F150" s="28"/>
+      <c r="G150" s="27"/>
+      <c r="H150" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
+++ b/Document/TR-1um_Drawing_Layer_DR_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCCECCD-2878-E140-B6F8-73D3EE4DA821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DEDE13-D27A-A84E-9F44-6EFB9E5FB4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="700" windowWidth="29380" windowHeight="18880" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
@@ -581,18 +581,6 @@
     <t>Bevel</t>
   </si>
   <si>
-    <t>WN-AC/AR related</t>
-  </si>
-  <si>
-    <t>AP/AN/DP/DN related</t>
-  </si>
-  <si>
-    <t>PC/CO related</t>
-  </si>
-  <si>
-    <t>BEOL related</t>
-  </si>
-  <si>
     <t>WN.Z1</t>
   </si>
   <si>
@@ -695,9 +683,6 @@
     <t>AA+GC+GR</t>
   </si>
   <si>
-    <t>AR/GR related</t>
-  </si>
-  <si>
     <t>GR.W1</t>
   </si>
   <si>
@@ -707,9 +692,6 @@
     <t>GR.S1</t>
   </si>
   <si>
-    <t>ESD related</t>
-  </si>
-  <si>
     <t>APE.WM</t>
   </si>
   <si>
@@ -809,9 +791,6 @@
     <t>ERWLMPE15</t>
   </si>
   <si>
-    <t>PAD related</t>
-  </si>
-  <si>
     <t>PO.W1</t>
   </si>
   <si>
@@ -923,9 +902,6 @@
     <t>PO.Z2</t>
   </si>
   <si>
-    <t>Prohibited</t>
-  </si>
-  <si>
     <t>PO.Z3</t>
   </si>
   <si>
@@ -947,9 +923,6 @@
     <t>CO.GG</t>
   </si>
   <si>
-    <t>Electrical / Optional</t>
-  </si>
-  <si>
     <t>ANTE</t>
   </si>
   <si>
@@ -966,6 +939,33 @@
   </si>
   <si>
     <t>WN.Z3</t>
+  </si>
+  <si>
+    <t>Cat-1: Prohibited</t>
+  </si>
+  <si>
+    <t>Cat-2:  WN-AC/AR related</t>
+  </si>
+  <si>
+    <t>Cat-3: AP/AN/DP/DN related</t>
+  </si>
+  <si>
+    <t>Cat-6: BEOL related</t>
+  </si>
+  <si>
+    <t>Cat-7: ESD related</t>
+  </si>
+  <si>
+    <t>Cat-8: PAD related</t>
+  </si>
+  <si>
+    <t>Cat-9: Electrical / Optional</t>
+  </si>
+  <si>
+    <t>Cat-5: AC/AR/GR related</t>
+  </si>
+  <si>
+    <t>Cat-4: GC/CO related</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1010,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1047,6 +1047,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1075,7 +1081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1165,6 +1171,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2062,10 +2080,10 @@
   <sheetData>
     <row r="2" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="22"/>
@@ -2098,7 +2116,7 @@
     </row>
     <row r="4" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>159</v>
@@ -2117,7 +2135,7 @@
     </row>
     <row r="5" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>160</v>
@@ -2136,7 +2154,7 @@
     </row>
     <row r="6" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>160</v>
@@ -2161,7 +2179,7 @@
         <v>146</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>171</v>
@@ -2231,10 +2249,10 @@
     </row>
     <row r="11" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>152</v>
@@ -2250,10 +2268,10 @@
     </row>
     <row r="12" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>156</v>
@@ -2269,16 +2287,16 @@
     </row>
     <row r="13" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F13" s="6">
         <v>0</v>
@@ -2288,10 +2306,10 @@
     </row>
     <row r="14" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B14" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>181</v>
+        <v>302</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="22"/>
@@ -2700,13 +2718,13 @@
     </row>
     <row r="34" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>136</v>
@@ -2716,7 +2734,7 @@
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2727,7 +2745,7 @@
         <v>138</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>165</v>
@@ -2740,10 +2758,10 @@
     </row>
     <row r="36" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B36" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>182</v>
+        <v>303</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="22"/>
@@ -2843,7 +2861,7 @@
         <v>141</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>135</v>
@@ -2866,7 +2884,7 @@
         <v>141</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>139</v>
@@ -2937,7 +2955,7 @@
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="29" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2948,7 +2966,7 @@
         <v>142</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>134</v>
@@ -3051,7 +3069,7 @@
         <v>144</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>135</v>
@@ -3074,7 +3092,7 @@
         <v>144</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>139</v>
@@ -3097,7 +3115,7 @@
         <v>143</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>136</v>
@@ -3145,7 +3163,7 @@
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="30" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3177,7 +3195,7 @@
         <v>145</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>134</v>
@@ -3192,10 +3210,10 @@
     </row>
     <row r="58" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B58" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>183</v>
+        <v>309</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="22"/>
@@ -3228,10 +3246,10 @@
     </row>
     <row r="60" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D60" s="13"/>
       <c r="E60" s="8" t="s">
@@ -3247,13 +3265,13 @@
     </row>
     <row r="61" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>134</v>
@@ -3268,10 +3286,10 @@
     </row>
     <row r="62" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>140</v>
@@ -3289,10 +3307,10 @@
     </row>
     <row r="63" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>143</v>
@@ -3310,44 +3328,44 @@
     </row>
     <row r="64" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F64" s="9">
         <v>1.2</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>144</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F65" s="9">
         <v>1.2</v>
       </c>
       <c r="G65" s="9"/>
       <c r="H65" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3474,13 +3492,13 @@
     </row>
     <row r="72" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="5" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>134</v>
@@ -3495,13 +3513,13 @@
     </row>
     <row r="73" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B73" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>136</v>
@@ -3516,10 +3534,10 @@
     </row>
     <row r="74" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B74" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>219</v>
+        <v>308</v>
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="22"/>
@@ -3555,10 +3573,10 @@
         <v>20</v>
       </c>
       <c r="C76" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>199</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>135</v>
@@ -3578,10 +3596,10 @@
         <v>115</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>139</v>
@@ -3598,10 +3616,10 @@
     </row>
     <row r="78" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>149</v>
@@ -3622,7 +3640,7 @@
         <v>124</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D79" s="13"/>
       <c r="E79" s="8" t="s">
@@ -3657,10 +3675,10 @@
     </row>
     <row r="81" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B81" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>143</v>
@@ -3678,13 +3696,13 @@
     </row>
     <row r="82" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>149</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>165</v>
@@ -3697,10 +3715,10 @@
     </row>
     <row r="83" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>159</v>
@@ -3716,13 +3734,13 @@
     </row>
     <row r="84" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C84" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D84" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>198</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>135</v>
@@ -3739,13 +3757,13 @@
     </row>
     <row r="85" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>139</v>
@@ -3762,13 +3780,13 @@
     </row>
     <row r="86" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>134</v>
@@ -3941,10 +3959,10 @@
     </row>
     <row r="95" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B95" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>184</v>
+        <v>304</v>
       </c>
       <c r="D95" s="23"/>
       <c r="E95" s="22"/>
@@ -4044,7 +4062,7 @@
         <v>152</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>148</v>
@@ -4183,13 +4201,13 @@
     </row>
     <row r="107" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C107" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E107" s="8" t="s">
         <v>134</v>
@@ -4307,10 +4325,10 @@
     </row>
     <row r="113" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B113" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>223</v>
+        <v>305</v>
       </c>
       <c r="D113" s="23"/>
       <c r="E113" s="22"/>
@@ -4343,13 +4361,13 @@
     </row>
     <row r="115" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B115" s="8" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E115" s="8" t="s">
         <v>135</v>
@@ -4366,13 +4384,13 @@
     </row>
     <row r="116" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B116" s="8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E116" s="8" t="s">
         <v>139</v>
@@ -4389,10 +4407,10 @@
     </row>
     <row r="117" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B117" s="8" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>143</v>
@@ -4405,15 +4423,15 @@
       </c>
       <c r="G117" s="9"/>
       <c r="H117" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B118" s="8" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D118" s="13" t="s">
         <v>180</v>
@@ -4426,15 +4444,15 @@
       </c>
       <c r="G118" s="9"/>
       <c r="H118" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="119" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B119" s="8" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>146</v>
@@ -4447,18 +4465,18 @@
       </c>
       <c r="G119" s="9"/>
       <c r="H119" s="8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B120" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>135</v>
@@ -4475,13 +4493,13 @@
     </row>
     <row r="121" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B121" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>139</v>
@@ -4498,10 +4516,10 @@
     </row>
     <row r="122" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B122" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D122" s="11" t="s">
         <v>140</v>
@@ -4514,15 +4532,15 @@
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B123" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D123" s="11" t="s">
         <v>180</v>
@@ -4535,15 +4553,15 @@
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B124" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D124" s="11" t="s">
         <v>146</v>
@@ -4556,15 +4574,15 @@
       </c>
       <c r="G124" s="6"/>
       <c r="H124" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B125" s="8" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D125" s="13"/>
       <c r="E125" s="8" t="s">
@@ -4575,18 +4593,18 @@
       </c>
       <c r="G125" s="9"/>
       <c r="H125" s="8" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B126" s="8" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>134</v>
@@ -4596,18 +4614,18 @@
       </c>
       <c r="G126" s="9"/>
       <c r="H126" s="8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B127" s="8" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>134</v>
@@ -4617,18 +4635,18 @@
       </c>
       <c r="G127" s="9"/>
       <c r="H127" s="8" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B128" s="8" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>134</v>
@@ -4638,15 +4656,15 @@
       </c>
       <c r="G128" s="9"/>
       <c r="H128" s="8" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B129" s="8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D129" s="13" t="s">
         <v>140</v>
@@ -4659,15 +4677,15 @@
       </c>
       <c r="G129" s="9"/>
       <c r="H129" s="8" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B130" s="8" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>143</v>
@@ -4680,15 +4698,15 @@
       </c>
       <c r="G130" s="9"/>
       <c r="H130" s="8" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="131" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B131" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>257</v>
+        <v>306</v>
       </c>
       <c r="D131" s="23"/>
       <c r="E131" s="22"/>
@@ -4721,10 +4739,10 @@
     </row>
     <row r="133" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B133" s="25" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C133" s="26" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D133" s="26"/>
       <c r="E133" s="25" t="s">
@@ -4735,18 +4753,18 @@
       </c>
       <c r="G133" s="27"/>
       <c r="H133" s="25" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="134" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B134" s="25" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C134" s="26" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E134" s="25" t="s">
         <v>134</v>
@@ -4756,18 +4774,18 @@
       </c>
       <c r="G134" s="27"/>
       <c r="H134" s="25" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="135" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B135" s="5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>148</v>
@@ -4777,18 +4795,18 @@
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B136" s="5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>148</v>
@@ -4798,18 +4816,18 @@
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="5" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="137" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B137" s="25" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C137" s="26" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D137" s="26" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E137" s="25" t="s">
         <v>136</v>
@@ -4819,15 +4837,15 @@
       </c>
       <c r="G137" s="27"/>
       <c r="H137" s="25" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B138" s="5" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D138" s="11" t="s">
         <v>140</v>
@@ -4840,15 +4858,15 @@
       </c>
       <c r="G138" s="6"/>
       <c r="H138" s="5" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="139" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B139" s="5" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D139" s="11" t="s">
         <v>143</v>
@@ -4861,18 +4879,18 @@
       </c>
       <c r="G139" s="6"/>
       <c r="H139" s="5" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="140" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B140" s="5" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>134</v>
@@ -4882,15 +4900,15 @@
       </c>
       <c r="G140" s="6"/>
       <c r="H140" s="5" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="141" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B141" s="5" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D141" s="11" t="s">
         <v>152</v>
@@ -4903,15 +4921,15 @@
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="25" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="142" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B142" s="5" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D142" s="11" t="s">
         <v>156</v>
@@ -4924,91 +4942,91 @@
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="25" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="143" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B143" s="5" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D143" s="11"/>
       <c r="E143" s="5" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="F143" s="6">
         <v>19</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="5" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B144" s="5" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D144" s="11"/>
       <c r="E144" s="5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F144" s="6">
         <v>40</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="5" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B145" s="5" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D145" s="11"/>
       <c r="E145" s="5" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="F145" s="6">
         <v>19</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="5" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B146" s="5" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D146" s="11"/>
       <c r="E146" s="5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F146" s="6">
         <v>40</v>
       </c>
       <c r="G146" s="6"/>
       <c r="H146" s="5" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="147" spans="2:8" ht="20" x14ac:dyDescent="0.2">
       <c r="B147" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D147" s="23"/>
       <c r="E147" s="22"/>
@@ -5040,30 +5058,30 @@
       </c>
     </row>
     <row r="149" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B149" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="C149" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="D149" s="26"/>
-      <c r="E149" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="F149" s="28">
+      <c r="B149" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="C149" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="D149" s="32"/>
+      <c r="E149" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="F149" s="33">
         <v>0</v>
       </c>
-      <c r="G149" s="27"/>
-      <c r="H149" s="25"/>
+      <c r="G149" s="34"/>
+      <c r="H149" s="31"/>
     </row>
     <row r="150" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B150" s="25"/>
-      <c r="C150" s="26"/>
-      <c r="D150" s="26"/>
-      <c r="E150" s="25"/>
-      <c r="F150" s="28"/>
-      <c r="G150" s="27"/>
-      <c r="H150" s="25"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="32"/>
+      <c r="D150" s="32"/>
+      <c r="E150" s="31"/>
+      <c r="F150" s="33"/>
+      <c r="G150" s="34"/>
+      <c r="H150" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
